--- a/docx/todo.xlsx
+++ b/docx/todo.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\vmmc_erp_frontend\docx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\Documents\GitHub\vmmc_erp_frontend\docx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A201EE-595A-4A84-A8B3-47FA359619CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7935A3-386A-4A48-BE0B-309D8F831332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18540" windowHeight="5940" xr2:uid="{EE8E3B1A-3261-4981-81FB-FDD5BBE0A7D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EE8E3B1A-3261-4981-81FB-FDD5BBE0A7D6}"/>
   </bookViews>
   <sheets>
     <sheet name="ui revamp" sheetId="2" r:id="rId1"/>
-    <sheet name="filters" sheetId="3" r:id="rId2"/>
-    <sheet name="auth password" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,63 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
-  <si>
-    <t>roles create</t>
-  </si>
-  <si>
-    <t>roles edit</t>
-  </si>
-  <si>
-    <t>offices create</t>
-  </si>
-  <si>
-    <t>offices edit</t>
-  </si>
-  <si>
-    <t>doc types create</t>
-  </si>
-  <si>
-    <t>doc types edit</t>
-  </si>
-  <si>
-    <t>doc tags create</t>
-  </si>
-  <si>
-    <t>doc tags edit</t>
-  </si>
-  <si>
-    <t>roles</t>
-  </si>
-  <si>
-    <t>offices</t>
-  </si>
-  <si>
-    <t>doc types</t>
-  </si>
-  <si>
-    <t>doc tags</t>
-  </si>
-  <si>
-    <t>audit trail</t>
-  </si>
-  <si>
-    <t>login</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>home page</t>
   </si>
   <si>
-    <t>navbar</t>
-  </si>
-  <si>
-    <t>footer</t>
-  </si>
-  <si>
-    <t>settings</t>
-  </si>
-  <si>
-    <t>admin dashboard</t>
+    <t>filter state</t>
   </si>
 </sst>
 </file>
@@ -119,11 +66,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,142 +382,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31EC63FA-497C-4377-8761-E43EEA9A183D}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F7711A-B53A-4DAD-9CF5-A08F2B6E9671}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A877F4-FE0D-42F5-88A2-103F6C61F62D}">
-  <dimension ref="A6:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
